--- a/Ehux.xlsx
+++ b/Ehux.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/y_f_bats_uu_nl/Documents/Documents/PhD/FluxModel/Rebuttal PP/GitHub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="345" documentId="11_44F17DD48F79A8D366075C52F37BD2721A48FBE5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD92C08A-788D-4DB4-A4C8-FC857D226462}"/>
+  <xr:revisionPtr revIDLastSave="346" documentId="11_44F17DD48F79A8D366075C52F37BD2721A48FBE5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AF0E9FB-DA7B-4C86-995C-AF7109055496}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -117,9 +117,6 @@
     <t>h</t>
   </si>
   <si>
-    <t>μmol/L</t>
-  </si>
-  <si>
     <t>cm^3</t>
   </si>
   <si>
@@ -163,6 +160,9 @@
   </si>
   <si>
     <t>10.1016/j.gca.2025.09.033</t>
+  </si>
+  <si>
+    <t>μmol/kg</t>
   </si>
 </sst>
 </file>
@@ -578,19 +578,19 @@
         <v>23</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
@@ -634,7 +634,7 @@
         <v>20</v>
       </c>
       <c r="Q2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
@@ -678,7 +678,7 @@
         <v>20</v>
       </c>
       <c r="Q3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
@@ -722,7 +722,7 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
@@ -766,7 +766,7 @@
         <v>20</v>
       </c>
       <c r="Q5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
@@ -810,7 +810,7 @@
         <v>20</v>
       </c>
       <c r="Q6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
@@ -854,7 +854,7 @@
         <v>20</v>
       </c>
       <c r="Q7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
@@ -898,7 +898,7 @@
         <v>20</v>
       </c>
       <c r="Q8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
@@ -942,7 +942,7 @@
         <v>20</v>
       </c>
       <c r="Q9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
@@ -986,7 +986,7 @@
         <v>20</v>
       </c>
       <c r="Q10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
@@ -1030,7 +1030,7 @@
         <v>20</v>
       </c>
       <c r="Q11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
@@ -1074,7 +1074,7 @@
         <v>19</v>
       </c>
       <c r="Q12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
@@ -1118,7 +1118,7 @@
         <v>19</v>
       </c>
       <c r="Q13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
@@ -1162,7 +1162,7 @@
         <v>19</v>
       </c>
       <c r="Q14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
@@ -1206,7 +1206,7 @@
         <v>19</v>
       </c>
       <c r="Q15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
@@ -1250,7 +1250,7 @@
         <v>19</v>
       </c>
       <c r="Q16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
@@ -1303,7 +1303,7 @@
         <v>18</v>
       </c>
       <c r="Q17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
@@ -1356,7 +1356,7 @@
         <v>18</v>
       </c>
       <c r="Q18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
@@ -1409,7 +1409,7 @@
         <v>18</v>
       </c>
       <c r="Q19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
@@ -1462,7 +1462,7 @@
         <v>18</v>
       </c>
       <c r="Q20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
@@ -1515,7 +1515,7 @@
         <v>18</v>
       </c>
       <c r="Q21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
@@ -1568,7 +1568,7 @@
         <v>18</v>
       </c>
       <c r="Q22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
@@ -1621,7 +1621,7 @@
         <v>18</v>
       </c>
       <c r="Q23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
@@ -1674,7 +1674,7 @@
         <v>18</v>
       </c>
       <c r="Q24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
@@ -1727,7 +1727,7 @@
         <v>18</v>
       </c>
       <c r="Q25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
@@ -1780,7 +1780,7 @@
         <v>18</v>
       </c>
       <c r="Q26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
@@ -1833,7 +1833,7 @@
         <v>18</v>
       </c>
       <c r="Q27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
@@ -1886,7 +1886,7 @@
         <v>18</v>
       </c>
       <c r="Q28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
@@ -1939,7 +1939,7 @@
         <v>18</v>
       </c>
       <c r="Q29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
@@ -1992,7 +1992,7 @@
         <v>18</v>
       </c>
       <c r="Q30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
@@ -2045,7 +2045,7 @@
         <v>18</v>
       </c>
       <c r="Q31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
@@ -2098,7 +2098,7 @@
         <v>18</v>
       </c>
       <c r="Q32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
@@ -2151,7 +2151,7 @@
         <v>18</v>
       </c>
       <c r="Q33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
@@ -2204,7 +2204,7 @@
         <v>18</v>
       </c>
       <c r="Q34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
@@ -2257,7 +2257,7 @@
         <v>18</v>
       </c>
       <c r="Q35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
@@ -2310,7 +2310,7 @@
         <v>18</v>
       </c>
       <c r="Q36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
@@ -2363,7 +2363,7 @@
         <v>18</v>
       </c>
       <c r="Q37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
@@ -2416,7 +2416,7 @@
         <v>18</v>
       </c>
       <c r="Q38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
@@ -2469,7 +2469,7 @@
         <v>18</v>
       </c>
       <c r="Q39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
@@ -2522,7 +2522,7 @@
         <v>18</v>
       </c>
       <c r="Q40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
@@ -2575,7 +2575,7 @@
         <v>18</v>
       </c>
       <c r="Q41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
@@ -2628,7 +2628,7 @@
         <v>18</v>
       </c>
       <c r="Q42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
@@ -2681,7 +2681,7 @@
         <v>18</v>
       </c>
       <c r="Q43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
@@ -2734,7 +2734,7 @@
         <v>18</v>
       </c>
       <c r="Q44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
@@ -2787,7 +2787,7 @@
         <v>18</v>
       </c>
       <c r="Q45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
@@ -2840,7 +2840,7 @@
         <v>18</v>
       </c>
       <c r="Q46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
@@ -2893,7 +2893,7 @@
         <v>18</v>
       </c>
       <c r="Q47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
@@ -2946,7 +2946,7 @@
         <v>18</v>
       </c>
       <c r="Q48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
@@ -2999,7 +2999,7 @@
         <v>18</v>
       </c>
       <c r="Q49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
@@ -3052,7 +3052,7 @@
         <v>18</v>
       </c>
       <c r="Q50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
@@ -3105,7 +3105,7 @@
         <v>18</v>
       </c>
       <c r="Q51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
@@ -3149,7 +3149,7 @@
         <v>17</v>
       </c>
       <c r="Q52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
@@ -3193,7 +3193,7 @@
         <v>17</v>
       </c>
       <c r="Q53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
@@ -3237,7 +3237,7 @@
         <v>17</v>
       </c>
       <c r="Q54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
@@ -3281,7 +3281,7 @@
         <v>17</v>
       </c>
       <c r="Q55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
@@ -3325,7 +3325,7 @@
         <v>17</v>
       </c>
       <c r="Q56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
@@ -3369,7 +3369,7 @@
         <v>17</v>
       </c>
       <c r="Q57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3415,13 +3415,13 @@
         <v>22</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -3429,37 +3429,37 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="I2" t="s">
-        <v>33</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
